--- a/examples/ltd-latest/Companysecretary.xlsx
+++ b/examples/ltd-latest/Companysecretary.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -171,14 +171,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="[$-F800]dddd&quot;, &quot;mmmm\ dd&quot;, &quot;yyyy"/>
-    <numFmt numFmtId="167" formatCode="General"/>
-    <numFmt numFmtId="168" formatCode="dd/mm/yy;@"/>
-    <numFmt numFmtId="169" formatCode="\£#,##0.00"/>
-    <numFmt numFmtId="170" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="167" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="168" formatCode="\£#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -304,7 +303,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -328,47 +327,47 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -376,7 +375,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -400,37 +399,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -504,7 +503,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.66"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="9.15"/>
@@ -653,8 +652,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW3"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="9" width="19.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="10" width="12.66"/>
@@ -664,7 +663,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="7" style="9" width="9.15"/>
   </cols>
   <sheetData>
-    <row r="1" s="13" customFormat="true" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
         <v>6</v>
       </c>
@@ -683,6 +682,257 @@
       <c r="F1" s="11" t="s">
         <v>11</v>
       </c>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="13"/>
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="13"/>
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+      <c r="AR1" s="13"/>
+      <c r="AS1" s="13"/>
+      <c r="AT1" s="13"/>
+      <c r="AU1" s="13"/>
+      <c r="AV1" s="13"/>
+      <c r="AW1" s="13"/>
+      <c r="AX1" s="13"/>
+      <c r="AY1" s="13"/>
+      <c r="AZ1" s="13"/>
+      <c r="BA1" s="13"/>
+      <c r="BB1" s="13"/>
+      <c r="BC1" s="13"/>
+      <c r="BD1" s="13"/>
+      <c r="BE1" s="13"/>
+      <c r="BF1" s="13"/>
+      <c r="BG1" s="13"/>
+      <c r="BH1" s="13"/>
+      <c r="BI1" s="13"/>
+      <c r="BJ1" s="13"/>
+      <c r="BK1" s="13"/>
+      <c r="BL1" s="13"/>
+      <c r="BM1" s="13"/>
+      <c r="BN1" s="13"/>
+      <c r="BO1" s="13"/>
+      <c r="BP1" s="13"/>
+      <c r="BQ1" s="13"/>
+      <c r="BR1" s="13"/>
+      <c r="BS1" s="13"/>
+      <c r="BT1" s="13"/>
+      <c r="BU1" s="13"/>
+      <c r="BV1" s="13"/>
+      <c r="BW1" s="13"/>
+      <c r="BX1" s="13"/>
+      <c r="BY1" s="13"/>
+      <c r="BZ1" s="13"/>
+      <c r="CA1" s="13"/>
+      <c r="CB1" s="13"/>
+      <c r="CC1" s="13"/>
+      <c r="CD1" s="13"/>
+      <c r="CE1" s="13"/>
+      <c r="CF1" s="13"/>
+      <c r="CG1" s="13"/>
+      <c r="CH1" s="13"/>
+      <c r="CI1" s="13"/>
+      <c r="CJ1" s="13"/>
+      <c r="CK1" s="13"/>
+      <c r="CL1" s="13"/>
+      <c r="CM1" s="13"/>
+      <c r="CN1" s="13"/>
+      <c r="CO1" s="13"/>
+      <c r="CP1" s="13"/>
+      <c r="CQ1" s="13"/>
+      <c r="CR1" s="13"/>
+      <c r="CS1" s="13"/>
+      <c r="CT1" s="13"/>
+      <c r="CU1" s="13"/>
+      <c r="CV1" s="13"/>
+      <c r="CW1" s="13"/>
+      <c r="CX1" s="13"/>
+      <c r="CY1" s="13"/>
+      <c r="CZ1" s="13"/>
+      <c r="DA1" s="13"/>
+      <c r="DB1" s="13"/>
+      <c r="DC1" s="13"/>
+      <c r="DD1" s="13"/>
+      <c r="DE1" s="13"/>
+      <c r="DF1" s="13"/>
+      <c r="DG1" s="13"/>
+      <c r="DH1" s="13"/>
+      <c r="DI1" s="13"/>
+      <c r="DJ1" s="13"/>
+      <c r="DK1" s="13"/>
+      <c r="DL1" s="13"/>
+      <c r="DM1" s="13"/>
+      <c r="DN1" s="13"/>
+      <c r="DO1" s="13"/>
+      <c r="DP1" s="13"/>
+      <c r="DQ1" s="13"/>
+      <c r="DR1" s="13"/>
+      <c r="DS1" s="13"/>
+      <c r="DT1" s="13"/>
+      <c r="DU1" s="13"/>
+      <c r="DV1" s="13"/>
+      <c r="DW1" s="13"/>
+      <c r="DX1" s="13"/>
+      <c r="DY1" s="13"/>
+      <c r="DZ1" s="13"/>
+      <c r="EA1" s="13"/>
+      <c r="EB1" s="13"/>
+      <c r="EC1" s="13"/>
+      <c r="ED1" s="13"/>
+      <c r="EE1" s="13"/>
+      <c r="EF1" s="13"/>
+      <c r="EG1" s="13"/>
+      <c r="EH1" s="13"/>
+      <c r="EI1" s="13"/>
+      <c r="EJ1" s="13"/>
+      <c r="EK1" s="13"/>
+      <c r="EL1" s="13"/>
+      <c r="EM1" s="13"/>
+      <c r="EN1" s="13"/>
+      <c r="EO1" s="13"/>
+      <c r="EP1" s="13"/>
+      <c r="EQ1" s="13"/>
+      <c r="ER1" s="13"/>
+      <c r="ES1" s="13"/>
+      <c r="ET1" s="13"/>
+      <c r="EU1" s="13"/>
+      <c r="EV1" s="13"/>
+      <c r="EW1" s="13"/>
+      <c r="EX1" s="13"/>
+      <c r="EY1" s="13"/>
+      <c r="EZ1" s="13"/>
+      <c r="FA1" s="13"/>
+      <c r="FB1" s="13"/>
+      <c r="FC1" s="13"/>
+      <c r="FD1" s="13"/>
+      <c r="FE1" s="13"/>
+      <c r="FF1" s="13"/>
+      <c r="FG1" s="13"/>
+      <c r="FH1" s="13"/>
+      <c r="FI1" s="13"/>
+      <c r="FJ1" s="13"/>
+      <c r="FK1" s="13"/>
+      <c r="FL1" s="13"/>
+      <c r="FM1" s="13"/>
+      <c r="FN1" s="13"/>
+      <c r="FO1" s="13"/>
+      <c r="FP1" s="13"/>
+      <c r="FQ1" s="13"/>
+      <c r="FR1" s="13"/>
+      <c r="FS1" s="13"/>
+      <c r="FT1" s="13"/>
+      <c r="FU1" s="13"/>
+      <c r="FV1" s="13"/>
+      <c r="FW1" s="13"/>
+      <c r="FX1" s="13"/>
+      <c r="FY1" s="13"/>
+      <c r="FZ1" s="13"/>
+      <c r="GA1" s="13"/>
+      <c r="GB1" s="13"/>
+      <c r="GC1" s="13"/>
+      <c r="GD1" s="13"/>
+      <c r="GE1" s="13"/>
+      <c r="GF1" s="13"/>
+      <c r="GG1" s="13"/>
+      <c r="GH1" s="13"/>
+      <c r="GI1" s="13"/>
+      <c r="GJ1" s="13"/>
+      <c r="GK1" s="13"/>
+      <c r="GL1" s="13"/>
+      <c r="GM1" s="13"/>
+      <c r="GN1" s="13"/>
+      <c r="GO1" s="13"/>
+      <c r="GP1" s="13"/>
+      <c r="GQ1" s="13"/>
+      <c r="GR1" s="13"/>
+      <c r="GS1" s="13"/>
+      <c r="GT1" s="13"/>
+      <c r="GU1" s="13"/>
+      <c r="GV1" s="13"/>
+      <c r="GW1" s="13"/>
+      <c r="GX1" s="13"/>
+      <c r="GY1" s="13"/>
+      <c r="GZ1" s="13"/>
+      <c r="HA1" s="13"/>
+      <c r="HB1" s="13"/>
+      <c r="HC1" s="13"/>
+      <c r="HD1" s="13"/>
+      <c r="HE1" s="13"/>
+      <c r="HF1" s="13"/>
+      <c r="HG1" s="13"/>
+      <c r="HH1" s="13"/>
+      <c r="HI1" s="13"/>
+      <c r="HJ1" s="13"/>
+      <c r="HK1" s="13"/>
+      <c r="HL1" s="13"/>
+      <c r="HM1" s="13"/>
+      <c r="HN1" s="13"/>
+      <c r="HO1" s="13"/>
+      <c r="HP1" s="13"/>
+      <c r="HQ1" s="13"/>
+      <c r="HR1" s="13"/>
+      <c r="HS1" s="13"/>
+      <c r="HT1" s="13"/>
+      <c r="HU1" s="13"/>
+      <c r="HV1" s="13"/>
+      <c r="HW1" s="13"/>
+      <c r="HX1" s="13"/>
+      <c r="HY1" s="13"/>
+      <c r="HZ1" s="13"/>
+      <c r="IA1" s="13"/>
+      <c r="IB1" s="13"/>
+      <c r="IC1" s="13"/>
+      <c r="ID1" s="13"/>
+      <c r="IE1" s="13"/>
+      <c r="IF1" s="13"/>
+      <c r="IG1" s="13"/>
+      <c r="IH1" s="13"/>
+      <c r="II1" s="13"/>
+      <c r="IJ1" s="13"/>
+      <c r="IK1" s="13"/>
+      <c r="IL1" s="13"/>
+      <c r="IM1" s="13"/>
+      <c r="IN1" s="13"/>
+      <c r="IO1" s="13"/>
+      <c r="IP1" s="13"/>
+      <c r="IQ1" s="13"/>
+      <c r="IR1" s="13"/>
+      <c r="IS1" s="13"/>
+      <c r="IT1" s="13"/>
+      <c r="IU1" s="13"/>
+      <c r="IV1" s="13"/>
+      <c r="IW1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
@@ -723,8 +973,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW5"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="18.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="20.66"/>
@@ -760,7 +1010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="13" customFormat="true" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
         <v>17</v>
       </c>
@@ -791,6 +1041,253 @@
       <c r="J2" s="11" t="s">
         <v>26</v>
       </c>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AC2" s="13"/>
+      <c r="AD2" s="13"/>
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="13"/>
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="13"/>
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+      <c r="AK2" s="13"/>
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="13"/>
+      <c r="AN2" s="13"/>
+      <c r="AO2" s="13"/>
+      <c r="AP2" s="13"/>
+      <c r="AQ2" s="13"/>
+      <c r="AR2" s="13"/>
+      <c r="AS2" s="13"/>
+      <c r="AT2" s="13"/>
+      <c r="AU2" s="13"/>
+      <c r="AV2" s="13"/>
+      <c r="AW2" s="13"/>
+      <c r="AX2" s="13"/>
+      <c r="AY2" s="13"/>
+      <c r="AZ2" s="13"/>
+      <c r="BA2" s="13"/>
+      <c r="BB2" s="13"/>
+      <c r="BC2" s="13"/>
+      <c r="BD2" s="13"/>
+      <c r="BE2" s="13"/>
+      <c r="BF2" s="13"/>
+      <c r="BG2" s="13"/>
+      <c r="BH2" s="13"/>
+      <c r="BI2" s="13"/>
+      <c r="BJ2" s="13"/>
+      <c r="BK2" s="13"/>
+      <c r="BL2" s="13"/>
+      <c r="BM2" s="13"/>
+      <c r="BN2" s="13"/>
+      <c r="BO2" s="13"/>
+      <c r="BP2" s="13"/>
+      <c r="BQ2" s="13"/>
+      <c r="BR2" s="13"/>
+      <c r="BS2" s="13"/>
+      <c r="BT2" s="13"/>
+      <c r="BU2" s="13"/>
+      <c r="BV2" s="13"/>
+      <c r="BW2" s="13"/>
+      <c r="BX2" s="13"/>
+      <c r="BY2" s="13"/>
+      <c r="BZ2" s="13"/>
+      <c r="CA2" s="13"/>
+      <c r="CB2" s="13"/>
+      <c r="CC2" s="13"/>
+      <c r="CD2" s="13"/>
+      <c r="CE2" s="13"/>
+      <c r="CF2" s="13"/>
+      <c r="CG2" s="13"/>
+      <c r="CH2" s="13"/>
+      <c r="CI2" s="13"/>
+      <c r="CJ2" s="13"/>
+      <c r="CK2" s="13"/>
+      <c r="CL2" s="13"/>
+      <c r="CM2" s="13"/>
+      <c r="CN2" s="13"/>
+      <c r="CO2" s="13"/>
+      <c r="CP2" s="13"/>
+      <c r="CQ2" s="13"/>
+      <c r="CR2" s="13"/>
+      <c r="CS2" s="13"/>
+      <c r="CT2" s="13"/>
+      <c r="CU2" s="13"/>
+      <c r="CV2" s="13"/>
+      <c r="CW2" s="13"/>
+      <c r="CX2" s="13"/>
+      <c r="CY2" s="13"/>
+      <c r="CZ2" s="13"/>
+      <c r="DA2" s="13"/>
+      <c r="DB2" s="13"/>
+      <c r="DC2" s="13"/>
+      <c r="DD2" s="13"/>
+      <c r="DE2" s="13"/>
+      <c r="DF2" s="13"/>
+      <c r="DG2" s="13"/>
+      <c r="DH2" s="13"/>
+      <c r="DI2" s="13"/>
+      <c r="DJ2" s="13"/>
+      <c r="DK2" s="13"/>
+      <c r="DL2" s="13"/>
+      <c r="DM2" s="13"/>
+      <c r="DN2" s="13"/>
+      <c r="DO2" s="13"/>
+      <c r="DP2" s="13"/>
+      <c r="DQ2" s="13"/>
+      <c r="DR2" s="13"/>
+      <c r="DS2" s="13"/>
+      <c r="DT2" s="13"/>
+      <c r="DU2" s="13"/>
+      <c r="DV2" s="13"/>
+      <c r="DW2" s="13"/>
+      <c r="DX2" s="13"/>
+      <c r="DY2" s="13"/>
+      <c r="DZ2" s="13"/>
+      <c r="EA2" s="13"/>
+      <c r="EB2" s="13"/>
+      <c r="EC2" s="13"/>
+      <c r="ED2" s="13"/>
+      <c r="EE2" s="13"/>
+      <c r="EF2" s="13"/>
+      <c r="EG2" s="13"/>
+      <c r="EH2" s="13"/>
+      <c r="EI2" s="13"/>
+      <c r="EJ2" s="13"/>
+      <c r="EK2" s="13"/>
+      <c r="EL2" s="13"/>
+      <c r="EM2" s="13"/>
+      <c r="EN2" s="13"/>
+      <c r="EO2" s="13"/>
+      <c r="EP2" s="13"/>
+      <c r="EQ2" s="13"/>
+      <c r="ER2" s="13"/>
+      <c r="ES2" s="13"/>
+      <c r="ET2" s="13"/>
+      <c r="EU2" s="13"/>
+      <c r="EV2" s="13"/>
+      <c r="EW2" s="13"/>
+      <c r="EX2" s="13"/>
+      <c r="EY2" s="13"/>
+      <c r="EZ2" s="13"/>
+      <c r="FA2" s="13"/>
+      <c r="FB2" s="13"/>
+      <c r="FC2" s="13"/>
+      <c r="FD2" s="13"/>
+      <c r="FE2" s="13"/>
+      <c r="FF2" s="13"/>
+      <c r="FG2" s="13"/>
+      <c r="FH2" s="13"/>
+      <c r="FI2" s="13"/>
+      <c r="FJ2" s="13"/>
+      <c r="FK2" s="13"/>
+      <c r="FL2" s="13"/>
+      <c r="FM2" s="13"/>
+      <c r="FN2" s="13"/>
+      <c r="FO2" s="13"/>
+      <c r="FP2" s="13"/>
+      <c r="FQ2" s="13"/>
+      <c r="FR2" s="13"/>
+      <c r="FS2" s="13"/>
+      <c r="FT2" s="13"/>
+      <c r="FU2" s="13"/>
+      <c r="FV2" s="13"/>
+      <c r="FW2" s="13"/>
+      <c r="FX2" s="13"/>
+      <c r="FY2" s="13"/>
+      <c r="FZ2" s="13"/>
+      <c r="GA2" s="13"/>
+      <c r="GB2" s="13"/>
+      <c r="GC2" s="13"/>
+      <c r="GD2" s="13"/>
+      <c r="GE2" s="13"/>
+      <c r="GF2" s="13"/>
+      <c r="GG2" s="13"/>
+      <c r="GH2" s="13"/>
+      <c r="GI2" s="13"/>
+      <c r="GJ2" s="13"/>
+      <c r="GK2" s="13"/>
+      <c r="GL2" s="13"/>
+      <c r="GM2" s="13"/>
+      <c r="GN2" s="13"/>
+      <c r="GO2" s="13"/>
+      <c r="GP2" s="13"/>
+      <c r="GQ2" s="13"/>
+      <c r="GR2" s="13"/>
+      <c r="GS2" s="13"/>
+      <c r="GT2" s="13"/>
+      <c r="GU2" s="13"/>
+      <c r="GV2" s="13"/>
+      <c r="GW2" s="13"/>
+      <c r="GX2" s="13"/>
+      <c r="GY2" s="13"/>
+      <c r="GZ2" s="13"/>
+      <c r="HA2" s="13"/>
+      <c r="HB2" s="13"/>
+      <c r="HC2" s="13"/>
+      <c r="HD2" s="13"/>
+      <c r="HE2" s="13"/>
+      <c r="HF2" s="13"/>
+      <c r="HG2" s="13"/>
+      <c r="HH2" s="13"/>
+      <c r="HI2" s="13"/>
+      <c r="HJ2" s="13"/>
+      <c r="HK2" s="13"/>
+      <c r="HL2" s="13"/>
+      <c r="HM2" s="13"/>
+      <c r="HN2" s="13"/>
+      <c r="HO2" s="13"/>
+      <c r="HP2" s="13"/>
+      <c r="HQ2" s="13"/>
+      <c r="HR2" s="13"/>
+      <c r="HS2" s="13"/>
+      <c r="HT2" s="13"/>
+      <c r="HU2" s="13"/>
+      <c r="HV2" s="13"/>
+      <c r="HW2" s="13"/>
+      <c r="HX2" s="13"/>
+      <c r="HY2" s="13"/>
+      <c r="HZ2" s="13"/>
+      <c r="IA2" s="13"/>
+      <c r="IB2" s="13"/>
+      <c r="IC2" s="13"/>
+      <c r="ID2" s="13"/>
+      <c r="IE2" s="13"/>
+      <c r="IF2" s="13"/>
+      <c r="IG2" s="13"/>
+      <c r="IH2" s="13"/>
+      <c r="II2" s="13"/>
+      <c r="IJ2" s="13"/>
+      <c r="IK2" s="13"/>
+      <c r="IL2" s="13"/>
+      <c r="IM2" s="13"/>
+      <c r="IN2" s="13"/>
+      <c r="IO2" s="13"/>
+      <c r="IP2" s="13"/>
+      <c r="IQ2" s="13"/>
+      <c r="IR2" s="13"/>
+      <c r="IS2" s="13"/>
+      <c r="IT2" s="13"/>
+      <c r="IU2" s="13"/>
+      <c r="IV2" s="13"/>
+      <c r="IW2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
@@ -870,7 +1367,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="20.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="19.66"/>
@@ -897,7 +1394,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
         <v>12</v>
       </c>
@@ -932,7 +1429,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="24" width="12.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="20.66"/>
